--- a/Configs/source/Datas/buff.xlsx
+++ b/Configs/source/Datas/buff.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="BuffTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -59,46 +59,61 @@
     <t>碎魂效果</t>
   </si>
   <si>
-    <t>最真实的自己</t>
+    <t>牺牲部分魂魄，换取敌人攻击落空。</t>
   </si>
   <si>
     <t>壮魂效果</t>
   </si>
   <si>
-    <t>戴上时施加死期</t>
+    <t>重拳出击！壮大自己的魂魄。</t>
   </si>
   <si>
     <t>返回本我效果</t>
   </si>
   <si>
-    <t>黑白无常</t>
+    <t>回合结束时神祇力量消散，返回原本的样子。</t>
   </si>
   <si>
     <t>死期</t>
   </si>
   <si>
-    <t>XXX</t>
+    <t>死期减少为0时死亡。</t>
   </si>
   <si>
     <t>黑无常</t>
   </si>
   <si>
+    <t>无视护甲，径直取命！</t>
+  </si>
+  <si>
     <t>白无常</t>
   </si>
   <si>
-    <t>拜托了 二郎神大人</t>
+    <t>攻击回血，勾魂随我！</t>
   </si>
   <si>
     <t>禁武令</t>
   </si>
   <si>
+    <t>“阴曹地府禁止斗殴！”攻击者将受到伤害。</t>
+  </si>
+  <si>
     <t>卸甲令</t>
   </si>
   <si>
+    <t>“孤魂野鬼禁止藏甲！”清空护甲，并且无法获得护甲。</t>
+  </si>
+  <si>
     <t>监禁令</t>
   </si>
   <si>
+    <t>“重大嫌疑实施逮捕！”下次行动失效。</t>
+  </si>
+  <si>
     <t>二郎神</t>
+  </si>
+  <si>
+    <t>“哮天犬，你去吧！”</t>
   </si>
 </sst>
 </file>
@@ -1096,13 +1111,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
-    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
-    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
+    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.975" customWidth="1"/>
+    <col min="4" max="4" width="15.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="11.6083333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1128,7 +1143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+    <row r="3" s="3" customFormat="1" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1141,7 +1156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:3">
+    <row r="5" spans="1:3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1149,7 +1164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="1:3">
       <c r="B6" t="s">
         <v>11</v>
       </c>
@@ -1157,7 +1172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:3">
+    <row r="7" spans="1:3">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1165,7 +1180,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:3">
+    <row r="8" spans="1:3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
@@ -1173,49 +1188,58 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:3">
+    <row r="9" spans="1:3">
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="2:3">
+        <v>21</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="2:3">
+        <v>23</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" spans="2:2">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="B14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="B15" s="6"/>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="1:3">
       <c r="B16" s="6"/>
     </row>
     <row r="17" spans="2:2">
